--- a/archives_mensuelles/2026-08_Août.xlsx
+++ b/archives_mensuelles/2026-08_Août.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>38,847 €</t>
+          <t>39,816 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,14 +772,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>14,744 €</t>
+          <t>15,350 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>24,104 €</t>
+          <t>24,466 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -8115,7 +8115,7 @@
         <v>725</v>
       </c>
       <c r="O103" s="17" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P103" s="13" t="n">
         <v>0</v>
@@ -8897,10 +8897,10 @@
         <v>1212</v>
       </c>
       <c r="O114" s="17" t="n">
-        <v>0</v>
+        <v>606</v>
       </c>
       <c r="P114" s="16" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
     </row>
     <row r="115">
@@ -12051,10 +12051,10 @@
         <v>46991.995</v>
       </c>
       <c r="O163" s="19" t="n">
-        <v>38847.212</v>
+        <v>39815.712</v>
       </c>
       <c r="P163" s="19" t="n">
-        <v>142.04</v>
+        <v>145.58</v>
       </c>
     </row>
   </sheetData>
@@ -13067,10 +13067,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>361327</v>
+        <v>360858</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>132769</v>
+        <v>132301</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>228558</v>
@@ -13092,10 +13092,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>165139</v>
+        <v>164533</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>61416</v>
+        <v>60810</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>103722</v>
@@ -13117,10 +13117,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>196188</v>
+        <v>196326</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>71353</v>
+        <v>71490</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>124835</v>
@@ -13669,7 +13669,7 @@
         </is>
       </c>
       <c r="I14" s="27" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15">
@@ -14005,7 +14005,7 @@
         </is>
       </c>
       <c r="I22" s="25" t="n">
-        <v>22198</v>
+        <v>22698</v>
       </c>
     </row>
     <row r="23">
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="I24" s="25" t="n">
-        <v>12162</v>
+        <v>12662</v>
       </c>
     </row>
   </sheetData>

--- a/archives_mensuelles/2026-08_Août.xlsx
+++ b/archives_mensuelles/2026-08_Août.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>39,816 €</t>
+          <t>40,393 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -779,7 +779,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>24,466 €</t>
+          <t>25,044 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P163"/>
+  <dimension ref="A1:P164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -5329,7 +5329,7 @@
         <v>1207</v>
       </c>
       <c r="O64" s="17" t="n">
-        <v>0</v>
+        <v>301.75</v>
       </c>
       <c r="P64" s="16" t="n">
         <v>0</v>
@@ -5770,62 +5770,70 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32565</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Afficher les AP signé avant MEP WFS</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J71" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L71" s="12" t="inlineStr"/>
-      <c r="M71" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L71" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32607</t>
+        </is>
+      </c>
+      <c r="M71" s="12" t="inlineStr">
+        <is>
+          <t>00163155</t>
+        </is>
+      </c>
       <c r="N71" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O71" s="13" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="P71" s="13" t="n">
         <v>0</v>
@@ -5834,12 +5842,12 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32565</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
@@ -5849,12 +5857,12 @@
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
@@ -5864,7 +5872,7 @@
       </c>
       <c r="G72" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H72" s="15" t="inlineStr">
@@ -5881,22 +5889,14 @@
         <v>4</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-32556</t>
-        </is>
-      </c>
-      <c r="M72" s="15" t="inlineStr">
-        <is>
-          <t>00162313</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L72" s="15" t="inlineStr"/>
+      <c r="M72" s="15" t="inlineStr"/>
       <c r="N72" s="16" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O72" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="16" t="n">
@@ -5906,32 +5906,32 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
@@ -5941,32 +5941,32 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J73" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M73" s="12" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N73" s="13" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O73" s="17" t="n">
         <v>0</v>
@@ -5978,32 +5978,32 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
@@ -6013,34 +6013,34 @@
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J74" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K74" s="15" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="16" t="n">
+        <v>2335</v>
+      </c>
+      <c r="O74" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="16" t="n">
@@ -6050,32 +6050,32 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -6085,34 +6085,34 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J75" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L75" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M75" s="12" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N75" s="13" t="n">
-        <v>450</v>
-      </c>
-      <c r="O75" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="13" t="n">
@@ -6122,32 +6122,32 @@
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
@@ -6157,65 +6157,69 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K76" s="15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O76" s="17" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C77" s="12" t="inlineStr"/>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
@@ -6225,64 +6229,60 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J77" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="L77" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M77" s="12" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N77" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="13" t="n">
-        <v>127.5</v>
+        <v>910</v>
+      </c>
+      <c r="O77" s="17" t="n">
+        <v>91</v>
       </c>
       <c r="P77" s="13" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
-        </is>
-      </c>
-      <c r="C78" s="15" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr"/>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
@@ -6309,52 +6309,52 @@
         <v>5</v>
       </c>
       <c r="K78" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O78" s="16" t="n">
-        <v>100</v>
+        <v>127.5</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J79" s="12" t="n">
@@ -6385,53 +6385,53 @@
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M79" s="12" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N79" s="13" t="n">
-        <v>590.15</v>
+        <v>0</v>
       </c>
       <c r="O79" s="13" t="n">
-        <v>793.65</v>
+        <v>100</v>
       </c>
       <c r="P79" s="13" t="n">
-        <v>3174.6</v>
+        <v>400</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
@@ -6446,64 +6446,64 @@
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K80" s="15" t="n">
-        <v>12.75</v>
+        <v>0.25</v>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>0</v>
+        <v>590.15</v>
       </c>
       <c r="O80" s="16" t="n">
-        <v>109.972</v>
+        <v>793.65</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>8.630000000000001</v>
+        <v>3174.6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -6513,69 +6513,69 @@
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J81" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="L81" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M81" s="12" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N81" s="13" t="n">
-        <v>285</v>
-      </c>
-      <c r="O81" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O81" s="13" t="n">
+        <v>109.972</v>
       </c>
       <c r="P81" s="13" t="n">
-        <v>0</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G82" s="15" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
@@ -6601,16 +6601,16 @@
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N82" s="16" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O82" s="17" t="n">
         <v>0</v>
@@ -6622,12 +6622,12 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J83" s="12" t="n">
@@ -6673,16 +6673,16 @@
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N83" s="13" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O83" s="17" t="n">
         <v>0</v>
@@ -6694,32 +6694,32 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G84" s="15" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="H84" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I84" s="15" t="inlineStr">
@@ -6741,52 +6741,52 @@
         <v>5</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O84" s="17" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>588</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
@@ -6801,49 +6801,49 @@
       </c>
       <c r="H85" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J85" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L85" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M85" s="12" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N85" s="13" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O85" s="17" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="P85" s="13" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J86" s="15" t="n">
@@ -6889,16 +6889,16 @@
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O86" s="17" t="n">
         <v>0</v>
@@ -6910,32 +6910,32 @@
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G87" s="12" t="inlineStr">
@@ -6945,49 +6945,49 @@
       </c>
       <c r="H87" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J87" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>15.25</v>
+        <v>0</v>
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N87" s="13" t="n">
-        <v>700</v>
-      </c>
-      <c r="O87" s="13" t="n">
-        <v>1934.1</v>
+        <v>300</v>
+      </c>
+      <c r="O87" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P87" s="13" t="n">
-        <v>126.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="G88" s="15" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H88" s="15" t="inlineStr">
@@ -7029,44 +7029,52 @@
         <v>6</v>
       </c>
       <c r="K88" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L88" s="15" t="inlineStr"/>
-      <c r="M88" s="15" t="inlineStr"/>
+        <v>15.25</v>
+      </c>
+      <c r="L88" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="M88" s="15" t="inlineStr">
+        <is>
+          <t>00157816</t>
+        </is>
+      </c>
       <c r="N88" s="16" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="O88" s="16" t="n">
-        <v>0</v>
+        <v>1934.1</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>0</v>
+        <v>126.83</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
@@ -7076,7 +7084,7 @@
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H89" s="12" t="inlineStr">
@@ -7086,64 +7094,56 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J89" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L89" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-31468</t>
-        </is>
-      </c>
-      <c r="M89" s="12" t="inlineStr">
-        <is>
-          <t>00157346</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L89" s="12" t="inlineStr"/>
+      <c r="M89" s="12" t="inlineStr"/>
       <c r="N89" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O89" s="13" t="n">
-        <v>138.825</v>
+        <v>0</v>
       </c>
       <c r="P89" s="13" t="n">
-        <v>15.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G90" s="15" t="inlineStr">
@@ -7153,49 +7153,49 @@
       </c>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K90" s="15" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>210</v>
-      </c>
-      <c r="O90" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O90" s="16" t="n">
+        <v>138.825</v>
       </c>
       <c r="P90" s="16" t="n">
-        <v>0</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J91" s="12" t="n">
@@ -7241,16 +7241,16 @@
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N91" s="13" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O91" s="17" t="n">
         <v>0</v>
@@ -7262,12 +7262,12 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
@@ -7313,16 +7313,16 @@
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O92" s="17" t="n">
         <v>0</v>
@@ -7334,12 +7334,12 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
@@ -7349,12 +7349,12 @@
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
@@ -7374,29 +7374,29 @@
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J93" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L93" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M93" s="12" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N93" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="13" t="n">
+        <v>255</v>
+      </c>
+      <c r="O93" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="13" t="n">
@@ -7406,12 +7406,12 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
@@ -7446,29 +7446,29 @@
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
-        <v>140</v>
-      </c>
-      <c r="O94" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="16" t="n">
@@ -7478,27 +7478,27 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30311</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAEN</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>GeODP - Modification des marges via activation Editique</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J95" s="12" t="n">
@@ -7529,19 +7529,19 @@
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30316</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr">
         <is>
-          <t>00154362</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N95" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="13" t="n">
-        <v>200</v>
+        <v>140</v>
+      </c>
+      <c r="O95" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P95" s="13" t="n">
         <v>0</v>
@@ -7550,32 +7550,32 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30311</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE CAEN</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G96" s="15" t="inlineStr">
@@ -7585,64 +7585,64 @@
       </c>
       <c r="H96" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30316</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154362</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>690</v>
-      </c>
-      <c r="O96" s="17" t="n">
-        <v>230</v>
+        <v>0</v>
+      </c>
+      <c r="O96" s="16" t="n">
+        <v>200</v>
       </c>
       <c r="P96" s="16" t="n">
-        <v>26.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30044</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>CD29</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Commande du flux WFS COM pour Inforoute</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H97" s="12" t="inlineStr">
@@ -7662,44 +7662,44 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J97" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>1</v>
+        <v>8.75</v>
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30046</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr">
         <is>
-          <t>00153621</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N97" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="13" t="n">
-        <v>0</v>
+        <v>690</v>
+      </c>
+      <c r="O97" s="17" t="n">
+        <v>230</v>
       </c>
       <c r="P97" s="13" t="n">
-        <v>0</v>
+        <v>26.29</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-30044</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>CD29</t>
         </is>
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="G98" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H98" s="15" t="inlineStr">
@@ -7734,23 +7734,23 @@
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-30046</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00153621</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
@@ -7766,12 +7766,12 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -7781,12 +7781,12 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
@@ -7806,33 +7806,33 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J99" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>2.42</v>
+        <v>0.25</v>
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N99" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O99" s="13" t="n">
-        <v>224.05</v>
+        <v>0</v>
       </c>
       <c r="P99" s="13" t="n">
-        <v>92.70999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -7889,22 +7889,22 @@
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O100" s="17" t="n">
-        <v>62.5</v>
+        <v>0</v>
+      </c>
+      <c r="O100" s="16" t="n">
+        <v>224.05</v>
       </c>
       <c r="P100" s="16" t="n">
-        <v>25.86</v>
+        <v>92.70999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -7961,47 +7961,49 @@
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O101" s="17" t="n">
-        <v>262.5</v>
+        <v>62.5</v>
       </c>
       <c r="P101" s="13" t="n">
-        <v>108.62</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E102" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
         <is>
@@ -8020,64 +8022,62 @@
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0.5</v>
+        <v>2.42</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" s="16" t="n">
-        <v>0</v>
+        <v>787.5</v>
+      </c>
+      <c r="O102" s="17" t="n">
+        <v>262.5</v>
       </c>
       <c r="P102" s="16" t="n">
-        <v>0</v>
+        <v>108.62</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
-        </is>
-      </c>
-      <c r="E103" s="12" t="inlineStr">
-        <is>
-          <t>Migration V2</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="n">
+        <v/>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G103" s="12" t="inlineStr">
@@ -8087,35 +8087,35 @@
       </c>
       <c r="H103" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J103" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
-        <v>725</v>
-      </c>
-      <c r="O103" s="17" t="n">
-        <v>362.5</v>
+        <v>0</v>
+      </c>
+      <c r="O103" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P103" s="13" t="n">
         <v>0</v>
@@ -8124,30 +8124,32 @@
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E104" s="15" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G104" s="15" t="inlineStr">
@@ -8157,49 +8159,49 @@
       </c>
       <c r="H104" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="16" t="n">
-        <v>1351.26</v>
+        <v>725</v>
+      </c>
+      <c r="O104" s="17" t="n">
+        <v>362.5</v>
       </c>
       <c r="P104" s="16" t="n">
-        <v>450.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
@@ -8209,13 +8211,11 @@
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E105" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v/>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
@@ -8234,33 +8234,33 @@
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J105" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O105" s="13" t="n">
-        <v>0</v>
+        <v>1351.26</v>
       </c>
       <c r="P105" s="13" t="n">
-        <v>0</v>
+        <v>450.42</v>
       </c>
     </row>
     <row r="106">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
@@ -8461,12 +8461,12 @@
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
@@ -8533,18 +8533,18 @@
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O109" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="13" t="n">
@@ -8554,12 +8554,12 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
@@ -8569,11 +8569,13 @@
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F110" s="15" t="inlineStr">
         <is>
@@ -8587,49 +8589,49 @@
       </c>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>4.25</v>
+        <v>1.95</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="16" t="n">
-        <v>98.28</v>
+        <v>1320</v>
+      </c>
+      <c r="O110" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
-        <v>23.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
@@ -8639,7 +8641,7 @@
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E111" s="12" t="n">
@@ -8657,65 +8659,63 @@
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J111" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>11.5</v>
+        <v>4.25</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N111" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O111" s="13" t="n">
-        <v>1280</v>
+        <v>98.28</v>
       </c>
       <c r="P111" s="13" t="n">
-        <v>111.3</v>
+        <v>23.12</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E112" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v/>
       </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
@@ -8734,58 +8734,60 @@
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>0.25</v>
+        <v>11.5</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O112" s="16" t="n">
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="P112" s="16" t="n">
-        <v>0</v>
+        <v>111.3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-25354</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - Déploiement Littéralis Standard</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Duncan HAMELIN</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE PLAN D'ORGON</t>
-        </is>
-      </c>
-      <c r="E113" s="12" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
@@ -8804,23 +8806,23 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>28/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-26768</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>00141775</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
@@ -8836,22 +8838,22 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-25354</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>Mairie de Plan d'Orgon  - Déploiement Littéralis Standard</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Duncan HAMELIN</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>MAIRIE DE PLAN D'ORGON</t>
         </is>
       </c>
       <c r="E114" s="15" t="n">
@@ -8874,60 +8876,58 @@
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>28/10/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
         <v>10</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26768</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00141775</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O114" s="17" t="n">
-        <v>606</v>
+        <v>0</v>
+      </c>
+      <c r="O114" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P114" s="16" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E115" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v/>
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
@@ -8946,59 +8946,59 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J115" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" s="13" t="n">
-        <v>0</v>
+        <v>1212</v>
+      </c>
+      <c r="O115" s="17" t="n">
+        <v>606</v>
       </c>
       <c r="P115" s="13" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E116" s="15" t="inlineStr">
         <is>
-          <t>Script purge de données</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F116" s="15" t="inlineStr">
@@ -9008,27 +9008,35 @@
       </c>
       <c r="G116" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H116" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L116" s="15" t="inlineStr"/>
-      <c r="M116" s="15" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L116" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27578</t>
+        </is>
+      </c>
+      <c r="M116" s="15" t="inlineStr">
+        <is>
+          <t>499043</t>
+        </is>
+      </c>
       <c r="N116" s="16" t="n">
         <v>0</v>
       </c>
@@ -9042,26 +9050,28 @@
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E117" s="12" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
@@ -9070,35 +9080,27 @@
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J117" s="12" t="n">
         <v>11</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L117" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27996</t>
-        </is>
-      </c>
-      <c r="M117" s="12" t="inlineStr">
-        <is>
-          <t>501219</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L117" s="12" t="inlineStr"/>
+      <c r="M117" s="12" t="inlineStr"/>
       <c r="N117" s="13" t="n">
         <v>0</v>
       </c>
@@ -9161,12 +9163,12 @@
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
@@ -9182,22 +9184,22 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E119" s="12" t="n">
@@ -9220,23 +9222,23 @@
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J119" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>3.25</v>
+        <v>0.5</v>
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
@@ -9252,12 +9254,12 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
@@ -9267,7 +9269,7 @@
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E120" s="15" t="n">
@@ -9290,23 +9292,23 @@
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>0.75</v>
+        <v>3.25</v>
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
@@ -9322,22 +9324,22 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
@@ -9355,28 +9357,28 @@
       </c>
       <c r="H121" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
         <v>13</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N121" s="13" t="n">
@@ -9392,22 +9394,22 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E122" s="15" t="n">
@@ -9425,28 +9427,28 @@
       </c>
       <c r="H122" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
         <v>13</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>1.31</v>
+        <v>0.25</v>
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N122" s="16" t="n">
@@ -9511,12 +9513,12 @@
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
@@ -9547,7 +9549,7 @@
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9581,12 +9583,12 @@
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
@@ -9617,7 +9619,7 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
@@ -9651,12 +9653,12 @@
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N125" s="13" t="n">
@@ -9672,22 +9674,22 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9705,34 +9707,34 @@
       </c>
       <c r="H126" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>0.5</v>
+        <v>1.31</v>
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N126" s="16" t="n">
-        <v>401</v>
-      </c>
-      <c r="O126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="16" t="n">
@@ -9742,22 +9744,22 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
@@ -9773,24 +9775,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H127" s="12" t="inlineStr"/>
+      <c r="H127" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K127" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="L127" s="12" t="inlineStr"/>
-      <c r="M127" s="12" t="inlineStr"/>
+      <c r="L127" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="M127" s="12" t="inlineStr">
+        <is>
+          <t>466234</t>
+        </is>
+      </c>
       <c r="N127" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O127" s="13" t="n">
+        <v>401</v>
+      </c>
+      <c r="O127" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="13" t="n">
@@ -9800,22 +9814,22 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E128" s="15" t="n">
@@ -9831,11 +9845,7 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H128" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H128" s="15" t="inlineStr"/>
       <c r="I128" s="15" t="inlineStr">
         <is>
           <t>23/04/2025</t>
@@ -9845,18 +9855,10 @@
         <v>16</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="L128" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28036</t>
-        </is>
-      </c>
-      <c r="M128" s="15" t="inlineStr">
-        <is>
-          <t>483799</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L128" s="15" t="inlineStr"/>
+      <c r="M128" s="15" t="inlineStr"/>
       <c r="N128" s="16" t="n">
         <v>0</v>
       </c>
@@ -9870,22 +9872,22 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
@@ -9903,28 +9905,28 @@
       </c>
       <c r="H129" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J129" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>0.5</v>
+        <v>8.25</v>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N129" s="13" t="n">
@@ -9940,22 +9942,22 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E130" s="15" t="n">
@@ -9978,29 +9980,29 @@
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N130" s="16" t="n">
-        <v>230</v>
-      </c>
-      <c r="O130" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P130" s="16" t="n">
@@ -10010,22 +10012,22 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E131" s="12" t="n">
@@ -10038,27 +10040,39 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H131" s="12" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H131" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L131" s="12" t="inlineStr"/>
-      <c r="M131" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L131" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M131" s="12" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N131" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" s="13" t="n">
+        <v>230</v>
+      </c>
+      <c r="O131" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P131" s="13" t="n">
@@ -10068,22 +10082,22 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E132" s="15" t="n">
@@ -10096,35 +10110,23 @@
       </c>
       <c r="G132" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H132" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H132" s="15" t="inlineStr"/>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
         <v>17</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L132" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M132" s="15" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L132" s="15" t="inlineStr"/>
+      <c r="M132" s="15" t="inlineStr"/>
       <c r="N132" s="16" t="n">
         <v>0</v>
       </c>
@@ -10138,12 +10140,12 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
@@ -10153,7 +10155,7 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10171,28 +10173,28 @@
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
         <v>17</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N133" s="13" t="n">
@@ -10208,22 +10210,22 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E134" s="15" t="n">
@@ -10241,28 +10243,28 @@
       </c>
       <c r="H134" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N134" s="16" t="n">
@@ -10327,12 +10329,12 @@
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N135" s="13" t="n">
@@ -10348,12 +10350,12 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
@@ -10363,7 +10365,7 @@
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E136" s="15" t="n">
@@ -10376,27 +10378,35 @@
       </c>
       <c r="G136" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H136" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J136" s="15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L136" s="15" t="inlineStr"/>
-      <c r="M136" s="15" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L136" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28214</t>
+        </is>
+      </c>
+      <c r="M136" s="15" t="inlineStr">
+        <is>
+          <t>458286</t>
+        </is>
+      </c>
       <c r="N136" s="16" t="n">
         <v>0</v>
       </c>
@@ -10410,22 +10420,22 @@
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E137" s="12" t="n">
@@ -10443,7 +10453,7 @@
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I137" s="12" t="inlineStr">
@@ -10455,7 +10465,7 @@
         <v>20</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>11.25</v>
+        <v>1</v>
       </c>
       <c r="L137" s="12" t="inlineStr"/>
       <c r="M137" s="12" t="inlineStr"/>
@@ -10472,12 +10482,12 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
@@ -10487,7 +10497,7 @@
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10510,14 +10520,14 @@
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
         <v>20</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>1.5</v>
+        <v>11.25</v>
       </c>
       <c r="L138" s="15" t="inlineStr"/>
       <c r="M138" s="15" t="inlineStr"/>
@@ -10534,22 +10544,22 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10557,44 +10567,36 @@
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H139" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
         <v>20</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M139" s="12" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L139" s="12" t="inlineStr"/>
+      <c r="M139" s="12" t="inlineStr"/>
       <c r="N139" s="13" t="n">
-        <v>240</v>
-      </c>
-      <c r="O139" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P139" s="13" t="n">
@@ -10604,22 +10606,22 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10627,7 +10629,7 @@
       </c>
       <c r="F140" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G140" s="15" t="inlineStr">
@@ -10637,34 +10639,34 @@
       </c>
       <c r="H140" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J140" s="15" t="n">
         <v>20</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M140" s="15" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N140" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O140" s="16" t="n">
+        <v>240</v>
+      </c>
+      <c r="O140" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P140" s="16" t="n">
@@ -10689,7 +10691,7 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10723,7 +10725,7 @@
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
@@ -10744,12 +10746,12 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
@@ -10759,7 +10761,7 @@
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10789,22 +10791,22 @@
         <v>20</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M142" s="15" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N142" s="16" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O142" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P142" s="16" t="n">
@@ -10814,22 +10816,22 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10842,7 +10844,7 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H143" s="12" t="inlineStr">
@@ -10852,21 +10854,29 @@
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L143" s="12" t="inlineStr"/>
-      <c r="M143" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L143" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M143" s="12" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N143" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O143" s="13" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O143" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P143" s="13" t="n">
@@ -10876,12 +10886,12 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-15041</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
@@ -10891,7 +10901,7 @@
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>CD38</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -10914,14 +10924,14 @@
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="L144" s="15" t="inlineStr"/>
       <c r="M144" s="15" t="inlineStr"/>
@@ -10938,22 +10948,22 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -10976,25 +10986,17 @@
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
         <v>28</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L145" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M145" s="12" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L145" s="12" t="inlineStr"/>
+      <c r="M145" s="12" t="inlineStr"/>
       <c r="N145" s="13" t="n">
         <v>0</v>
       </c>
@@ -11008,22 +11010,22 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
@@ -11046,17 +11048,25 @@
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L146" s="15" t="inlineStr"/>
-      <c r="M146" s="15" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L146" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M146" s="15" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N146" s="16" t="n">
         <v>0</v>
       </c>
@@ -11070,22 +11080,22 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
@@ -11108,14 +11118,14 @@
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L147" s="12" t="inlineStr"/>
       <c r="M147" s="12" t="inlineStr"/>
@@ -11132,12 +11142,12 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
@@ -11147,7 +11157,7 @@
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E148" s="15" t="n">
@@ -11165,19 +11175,19 @@
       </c>
       <c r="H148" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
         <v>33</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L148" s="15" t="inlineStr"/>
       <c r="M148" s="15" t="inlineStr"/>
@@ -11194,22 +11204,22 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
@@ -11232,14 +11242,14 @@
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L149" s="12" t="inlineStr"/>
       <c r="M149" s="12" t="inlineStr"/>
@@ -11256,22 +11266,22 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E150" s="15" t="n">
@@ -11284,35 +11294,27 @@
       </c>
       <c r="G150" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H150" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I150" s="15" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J150" s="15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L150" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M150" s="15" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L150" s="15" t="inlineStr"/>
+      <c r="M150" s="15" t="inlineStr"/>
       <c r="N150" s="16" t="n">
         <v>0</v>
       </c>
@@ -11326,22 +11328,22 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E151" s="12" t="n">
@@ -11354,23 +11356,35 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H151" s="12" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H151" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I151" s="12" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J151" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L151" s="12" t="inlineStr"/>
-      <c r="M151" s="12" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L151" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M151" s="12" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N151" s="13" t="n">
         <v>0</v>
       </c>
@@ -11384,12 +11398,12 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr">
@@ -11399,7 +11413,7 @@
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E152" s="15" t="n">
@@ -11415,14 +11429,10 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H152" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H152" s="15" t="inlineStr"/>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
@@ -11431,16 +11441,8 @@
       <c r="K152" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="L152" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M152" s="15" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+      <c r="L152" s="15" t="inlineStr"/>
+      <c r="M152" s="15" t="inlineStr"/>
       <c r="N152" s="16" t="n">
         <v>0</v>
       </c>
@@ -11454,12 +11456,12 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
@@ -11469,7 +11471,7 @@
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E153" s="12" t="n">
@@ -11492,17 +11494,25 @@
       </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L153" s="12" t="inlineStr"/>
-      <c r="M153" s="12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L153" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M153" s="12" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N153" s="13" t="n">
         <v>0</v>
       </c>
@@ -11516,28 +11526,26 @@
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E154" s="15" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E154" s="15" t="n">
+        <v/>
       </c>
       <c r="F154" s="15" t="inlineStr">
         <is>
@@ -11551,7 +11559,7 @@
       </c>
       <c r="H154" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I154" s="15" t="inlineStr">
@@ -11563,7 +11571,7 @@
         <v>35</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="L154" s="15" t="inlineStr"/>
       <c r="M154" s="15" t="inlineStr"/>
@@ -11580,23 +11588,27 @@
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C155" s="12" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C155" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E155" s="12" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F155" s="12" t="inlineStr">
@@ -11611,19 +11623,19 @@
       </c>
       <c r="H155" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I155" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J155" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>11</v>
+        <v>1.25</v>
       </c>
       <c r="L155" s="12" t="inlineStr"/>
       <c r="M155" s="12" t="inlineStr"/>
@@ -11640,27 +11652,23 @@
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
-        </is>
-      </c>
-      <c r="C156" s="15" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C156" s="15" t="inlineStr"/>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>MONTPELLIER MMM</t>
         </is>
       </c>
       <c r="E156" s="15" t="inlineStr">
         <is>
-          <t>Montée de version + Pastell</t>
+          <t>Déploiement Module AC</t>
         </is>
       </c>
       <c r="F156" s="15" t="inlineStr">
@@ -11675,19 +11683,19 @@
       </c>
       <c r="H156" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J156" s="15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>0.5</v>
+        <v>11</v>
       </c>
       <c r="L156" s="15" t="inlineStr"/>
       <c r="M156" s="15" t="inlineStr"/>
@@ -11704,21 +11712,29 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="C157" s="12" t="inlineStr"/>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="E157" s="12" t="inlineStr"/>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E157" s="12" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11726,17 +11742,21 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H157" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H157" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J157" s="12" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K157" s="12" t="n">
         <v>0.5</v>
@@ -11756,18 +11776,18 @@
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr"/>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E158" s="15" t="inlineStr"/>
@@ -11784,14 +11804,14 @@
       <c r="H158" s="15" t="inlineStr"/>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J158" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K158" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L158" s="15" t="inlineStr"/>
       <c r="M158" s="15" t="inlineStr"/>
@@ -11808,18 +11828,18 @@
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr"/>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E159" s="12" t="inlineStr"/>
@@ -11830,36 +11850,28 @@
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H159" s="12" t="inlineStr"/>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J159" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M159" s="12" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L159" s="12" t="inlineStr"/>
+      <c r="M159" s="12" t="inlineStr"/>
       <c r="N159" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O159" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P159" s="13" t="n">
         <v>0</v>
@@ -11868,18 +11880,18 @@
     <row r="160">
       <c r="A160" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C160" s="15" t="inlineStr"/>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E160" s="15" t="inlineStr"/>
@@ -11896,50 +11908,50 @@
       <c r="H160" s="15" t="inlineStr"/>
       <c r="I160" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J160" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K160" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L160" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-34778</t>
         </is>
       </c>
       <c r="M160" s="15" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00172868</t>
         </is>
       </c>
       <c r="N160" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O160" s="16" t="n">
-        <v>595.7</v>
+        <v>100</v>
       </c>
       <c r="P160" s="16" t="n">
-        <v>595.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr"/>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E161" s="12" t="inlineStr"/>
@@ -11950,48 +11962,56 @@
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H161" s="12" t="inlineStr"/>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J161" s="12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K161" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L161" s="12" t="inlineStr"/>
-      <c r="M161" s="12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L161" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M161" s="12" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N161" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O161" s="13" t="n">
-        <v>0</v>
+        <v>595.7</v>
       </c>
       <c r="P161" s="13" t="n">
-        <v>0</v>
+        <v>595.7</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
         <is>
-          <t>PSC-583</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr"/>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E162" s="15" t="inlineStr"/>
@@ -12008,11 +12028,11 @@
       <c r="H162" s="15" t="inlineStr"/>
       <c r="I162" s="15" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J162" s="15" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K162" s="15" t="n">
         <v>0.25</v>
@@ -12030,31 +12050,83 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="18" t="inlineStr">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>PSC-583</t>
+        </is>
+      </c>
+      <c r="B163" s="12" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="C163" s="12" t="inlineStr"/>
+      <c r="D163" s="12" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="E163" s="12" t="inlineStr"/>
+      <c r="F163" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G163" s="12" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H163" s="12" t="inlineStr"/>
+      <c r="I163" s="12" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J163" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K163" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L163" s="12" t="inlineStr"/>
+      <c r="M163" s="12" t="inlineStr"/>
+      <c r="N163" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B163" s="18" t="inlineStr"/>
-      <c r="C163" s="18" t="inlineStr"/>
-      <c r="D163" s="18" t="inlineStr"/>
-      <c r="E163" s="18" t="inlineStr"/>
-      <c r="F163" s="18" t="inlineStr"/>
-      <c r="G163" s="18" t="inlineStr"/>
-      <c r="H163" s="18" t="inlineStr"/>
-      <c r="I163" s="18" t="inlineStr"/>
-      <c r="J163" s="18" t="inlineStr"/>
-      <c r="K163" s="18" t="inlineStr"/>
-      <c r="L163" s="18" t="inlineStr"/>
-      <c r="M163" s="18" t="inlineStr"/>
-      <c r="N163" s="19" t="n">
+      <c r="B164" s="18" t="inlineStr"/>
+      <c r="C164" s="18" t="inlineStr"/>
+      <c r="D164" s="18" t="inlineStr"/>
+      <c r="E164" s="18" t="inlineStr"/>
+      <c r="F164" s="18" t="inlineStr"/>
+      <c r="G164" s="18" t="inlineStr"/>
+      <c r="H164" s="18" t="inlineStr"/>
+      <c r="I164" s="18" t="inlineStr"/>
+      <c r="J164" s="18" t="inlineStr"/>
+      <c r="K164" s="18" t="inlineStr"/>
+      <c r="L164" s="18" t="inlineStr"/>
+      <c r="M164" s="18" t="inlineStr"/>
+      <c r="N164" s="19" t="n">
         <v>46991.995</v>
       </c>
-      <c r="O163" s="19" t="n">
-        <v>39815.712</v>
-      </c>
-      <c r="P163" s="19" t="n">
-        <v>145.58</v>
+      <c r="O164" s="19" t="n">
+        <v>40393.462</v>
+      </c>
+      <c r="P164" s="19" t="n">
+        <v>147.69</v>
       </c>
     </row>
   </sheetData>
@@ -12218,6 +12290,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId159"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13067,16 +13140,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>360858</v>
+        <v>362786</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>132301</v>
+        <v>134530</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>228558</v>
+        <v>228256</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>145176</v>
+        <v>144874</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>21179</v>
@@ -13117,16 +13190,16 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>196326</v>
+        <v>198253</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>71490</v>
+        <v>73719</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>124835</v>
+        <v>124534</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>58546</v>
+        <v>58244</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>9871</v>
@@ -13624,7 +13697,7 @@
         </is>
       </c>
       <c r="I13" s="26" t="n">
-        <v>0</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="14">
@@ -14005,7 +14078,7 @@
         </is>
       </c>
       <c r="I22" s="25" t="n">
-        <v>22698</v>
+        <v>25202</v>
       </c>
     </row>
     <row r="23">
@@ -14047,7 +14120,7 @@
         </is>
       </c>
       <c r="I24" s="25" t="n">
-        <v>12662</v>
+        <v>15166</v>
       </c>
     </row>
   </sheetData>

--- a/archives_mensuelles/2026-08_Août.xlsx
+++ b/archives_mensuelles/2026-08_Août.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>40,393 €</t>
+          <t>40,643 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>81.3%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,7 +772,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>15,350 €</t>
+          <t>15,600 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P164"/>
+  <dimension ref="A1:P166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -7694,27 +7694,27 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30044</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>CD29</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>Commande du flux WFS COM pour Inforoute</t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="G98" s="15" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H98" s="15" t="inlineStr">
@@ -7741,23 +7741,23 @@
         <v>7</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30046</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00153621</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O98" s="16" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="P98" s="16" t="n">
         <v>0</v>
@@ -7766,12 +7766,12 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-30044</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -7781,12 +7781,12 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>CD29</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H99" s="12" t="inlineStr">
@@ -7806,23 +7806,23 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J99" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-30046</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00153621</t>
         </is>
       </c>
       <c r="N99" s="13" t="n">
@@ -7838,12 +7838,12 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
@@ -7853,12 +7853,12 @@
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E100" s="15" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F100" s="15" t="inlineStr">
@@ -7878,33 +7878,33 @@
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K100" s="15" t="n">
-        <v>2.42</v>
+        <v>0.25</v>
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O100" s="16" t="n">
-        <v>224.05</v>
+        <v>0</v>
       </c>
       <c r="P100" s="16" t="n">
-        <v>92.70999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -7961,22 +7961,22 @@
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O101" s="17" t="n">
-        <v>62.5</v>
+        <v>0</v>
+      </c>
+      <c r="O101" s="13" t="n">
+        <v>224.05</v>
       </c>
       <c r="P101" s="13" t="n">
-        <v>25.86</v>
+        <v>92.70999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -8033,47 +8033,49 @@
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O102" s="17" t="n">
-        <v>262.5</v>
+        <v>62.5</v>
       </c>
       <c r="P102" s="16" t="n">
-        <v>108.62</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E103" s="12" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
@@ -8092,64 +8094,62 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J103" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>0.5</v>
+        <v>2.42</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="13" t="n">
-        <v>0</v>
+        <v>787.5</v>
+      </c>
+      <c r="O103" s="17" t="n">
+        <v>262.5</v>
       </c>
       <c r="P103" s="13" t="n">
-        <v>0</v>
+        <v>108.62</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
-        </is>
-      </c>
-      <c r="E104" s="15" t="inlineStr">
-        <is>
-          <t>Migration V2</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v/>
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G104" s="15" t="inlineStr">
@@ -8159,35 +8159,35 @@
       </c>
       <c r="H104" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>725</v>
-      </c>
-      <c r="O104" s="17" t="n">
-        <v>362.5</v>
+        <v>0</v>
+      </c>
+      <c r="O104" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P104" s="16" t="n">
         <v>0</v>
@@ -8196,30 +8196,32 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E105" s="12" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G105" s="12" t="inlineStr">
@@ -8229,49 +8231,49 @@
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J105" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="13" t="n">
-        <v>1351.26</v>
+        <v>725</v>
+      </c>
+      <c r="O105" s="17" t="n">
+        <v>362.5</v>
       </c>
       <c r="P105" s="13" t="n">
-        <v>450.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
@@ -8281,13 +8283,11 @@
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E106" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v/>
       </c>
       <c r="F106" s="15" t="inlineStr">
         <is>
@@ -8306,33 +8306,33 @@
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O106" s="16" t="n">
-        <v>0</v>
+        <v>1351.26</v>
       </c>
       <c r="P106" s="16" t="n">
-        <v>0</v>
+        <v>450.42</v>
       </c>
     </row>
     <row r="107">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
@@ -8461,12 +8461,12 @@
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
@@ -8605,18 +8605,18 @@
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O110" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
@@ -8626,12 +8626,12 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
@@ -8641,11 +8641,13 @@
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E111" s="12" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
@@ -8659,49 +8661,49 @@
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J111" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>4.25</v>
+        <v>1.95</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N111" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O111" s="13" t="n">
-        <v>98.28</v>
+        <v>1320</v>
+      </c>
+      <c r="O111" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P111" s="13" t="n">
-        <v>23.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
@@ -8711,7 +8713,7 @@
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E112" s="15" t="n">
@@ -8729,65 +8731,63 @@
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>11.5</v>
+        <v>4.25</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O112" s="16" t="n">
-        <v>1280</v>
+        <v>98.28</v>
       </c>
       <c r="P112" s="16" t="n">
-        <v>111.3</v>
+        <v>23.12</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E113" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v/>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
@@ -8806,58 +8806,60 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>0.25</v>
+        <v>11.5</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O113" s="13" t="n">
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="P113" s="13" t="n">
-        <v>0</v>
+        <v>111.3</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-25354</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - Déploiement Littéralis Standard</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Duncan HAMELIN</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE PLAN D'ORGON</t>
-        </is>
-      </c>
-      <c r="E114" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E114" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F114" s="15" t="inlineStr">
         <is>
@@ -8876,23 +8878,23 @@
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>28/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26768</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>00141775</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
@@ -8908,22 +8910,22 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-25354</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>Mairie de Plan d'Orgon  - Déploiement Littéralis Standard</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Duncan HAMELIN</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>MAIRIE DE PLAN D'ORGON</t>
         </is>
       </c>
       <c r="E115" s="12" t="n">
@@ -8946,60 +8948,58 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>28/10/2025</t>
         </is>
       </c>
       <c r="J115" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26768</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00141775</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O115" s="17" t="n">
-        <v>606</v>
+        <v>0</v>
+      </c>
+      <c r="O115" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P115" s="13" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E116" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v/>
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
@@ -9018,59 +9018,59 @@
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
         <v>10</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O116" s="16" t="n">
-        <v>0</v>
+        <v>1212</v>
+      </c>
+      <c r="O116" s="17" t="n">
+        <v>606</v>
       </c>
       <c r="P116" s="16" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Script purge de données</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
@@ -9080,27 +9080,35 @@
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J117" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L117" s="12" t="inlineStr"/>
-      <c r="M117" s="12" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L117" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27578</t>
+        </is>
+      </c>
+      <c r="M117" s="12" t="inlineStr">
+        <is>
+          <t>499043</t>
+        </is>
+      </c>
       <c r="N117" s="13" t="n">
         <v>0</v>
       </c>
@@ -9114,26 +9122,28 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E118" s="15" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
@@ -9142,35 +9152,27 @@
       </c>
       <c r="G118" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
         <v>11</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L118" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27996</t>
-        </is>
-      </c>
-      <c r="M118" s="15" t="inlineStr">
-        <is>
-          <t>501219</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L118" s="15" t="inlineStr"/>
+      <c r="M118" s="15" t="inlineStr"/>
       <c r="N118" s="16" t="n">
         <v>0</v>
       </c>
@@ -9233,12 +9235,12 @@
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
@@ -9254,22 +9256,22 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E120" s="15" t="n">
@@ -9292,23 +9294,23 @@
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>3.25</v>
+        <v>0.5</v>
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
@@ -9324,12 +9326,12 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
@@ -9339,7 +9341,7 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
@@ -9362,23 +9364,23 @@
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>0.75</v>
+        <v>3.25</v>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N121" s="13" t="n">
@@ -9394,22 +9396,22 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E122" s="15" t="n">
@@ -9427,28 +9429,28 @@
       </c>
       <c r="H122" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
         <v>13</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N122" s="16" t="n">
@@ -9464,22 +9466,22 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E123" s="12" t="n">
@@ -9497,28 +9499,28 @@
       </c>
       <c r="H123" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J123" s="12" t="n">
         <v>13</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>1.31</v>
+        <v>0.25</v>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
@@ -9583,12 +9585,12 @@
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
@@ -9619,7 +9621,7 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
@@ -9653,12 +9655,12 @@
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N125" s="13" t="n">
@@ -9689,7 +9691,7 @@
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9723,12 +9725,12 @@
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N126" s="16" t="n">
@@ -9744,22 +9746,22 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
@@ -9777,34 +9779,34 @@
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>0.5</v>
+        <v>1.31</v>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N127" s="13" t="n">
-        <v>401</v>
-      </c>
-      <c r="O127" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="13" t="n">
@@ -9814,22 +9816,22 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E128" s="15" t="n">
@@ -9845,24 +9847,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H128" s="15" t="inlineStr"/>
+      <c r="H128" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K128" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="L128" s="15" t="inlineStr"/>
-      <c r="M128" s="15" t="inlineStr"/>
+      <c r="L128" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="M128" s="15" t="inlineStr">
+        <is>
+          <t>466234</t>
+        </is>
+      </c>
       <c r="N128" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" s="16" t="n">
+        <v>401</v>
+      </c>
+      <c r="O128" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="16" t="n">
@@ -9872,22 +9886,22 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
@@ -9903,11 +9917,7 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H129" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H129" s="12" t="inlineStr"/>
       <c r="I129" s="12" t="inlineStr">
         <is>
           <t>23/04/2025</t>
@@ -9917,18 +9927,10 @@
         <v>16</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="L129" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28036</t>
-        </is>
-      </c>
-      <c r="M129" s="12" t="inlineStr">
-        <is>
-          <t>483799</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L129" s="12" t="inlineStr"/>
+      <c r="M129" s="12" t="inlineStr"/>
       <c r="N129" s="13" t="n">
         <v>0</v>
       </c>
@@ -9942,22 +9944,22 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E130" s="15" t="n">
@@ -9975,28 +9977,28 @@
       </c>
       <c r="H130" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>0.5</v>
+        <v>8.25</v>
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N130" s="16" t="n">
@@ -10012,22 +10014,22 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E131" s="12" t="n">
@@ -10050,29 +10052,29 @@
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N131" s="13" t="n">
-        <v>230</v>
-      </c>
-      <c r="O131" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P131" s="13" t="n">
@@ -10082,22 +10084,22 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E132" s="15" t="n">
@@ -10110,27 +10112,39 @@
       </c>
       <c r="G132" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H132" s="15" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H132" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L132" s="15" t="inlineStr"/>
-      <c r="M132" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L132" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M132" s="15" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N132" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O132" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O132" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P132" s="16" t="n">
@@ -10140,22 +10154,22 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10168,35 +10182,23 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H133" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H133" s="12" t="inlineStr"/>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
         <v>17</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L133" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M133" s="12" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L133" s="12" t="inlineStr"/>
+      <c r="M133" s="12" t="inlineStr"/>
       <c r="N133" s="13" t="n">
         <v>0</v>
       </c>
@@ -10210,12 +10212,12 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
@@ -10225,7 +10227,7 @@
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E134" s="15" t="n">
@@ -10243,28 +10245,28 @@
       </c>
       <c r="H134" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
         <v>17</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N134" s="16" t="n">
@@ -10280,22 +10282,22 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
@@ -10313,28 +10315,28 @@
       </c>
       <c r="H135" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I135" s="12" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J135" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N135" s="13" t="n">
@@ -10399,12 +10401,12 @@
       </c>
       <c r="L136" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M136" s="15" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N136" s="16" t="n">
@@ -10420,12 +10422,12 @@
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
@@ -10435,7 +10437,7 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E137" s="12" t="n">
@@ -10448,27 +10450,35 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J137" s="12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L137" s="12" t="inlineStr"/>
-      <c r="M137" s="12" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L137" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28214</t>
+        </is>
+      </c>
+      <c r="M137" s="12" t="inlineStr">
+        <is>
+          <t>458286</t>
+        </is>
+      </c>
       <c r="N137" s="13" t="n">
         <v>0</v>
       </c>
@@ -10482,22 +10492,22 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10515,7 +10525,7 @@
       </c>
       <c r="H138" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I138" s="15" t="inlineStr">
@@ -10527,7 +10537,7 @@
         <v>20</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>11.25</v>
+        <v>1</v>
       </c>
       <c r="L138" s="15" t="inlineStr"/>
       <c r="M138" s="15" t="inlineStr"/>
@@ -10544,12 +10554,12 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
@@ -10559,7 +10569,7 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10582,14 +10592,14 @@
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
         <v>20</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>1.5</v>
+        <v>11.25</v>
       </c>
       <c r="L139" s="12" t="inlineStr"/>
       <c r="M139" s="12" t="inlineStr"/>
@@ -10606,22 +10616,22 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10629,44 +10639,36 @@
       </c>
       <c r="F140" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G140" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H140" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J140" s="15" t="n">
         <v>20</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M140" s="15" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L140" s="15" t="inlineStr"/>
+      <c r="M140" s="15" t="inlineStr"/>
       <c r="N140" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O140" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P140" s="16" t="n">
@@ -10676,22 +10678,22 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10699,7 +10701,7 @@
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G141" s="12" t="inlineStr">
@@ -10709,34 +10711,34 @@
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
         <v>20</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N141" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O141" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="O141" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P141" s="13" t="n">
@@ -10761,7 +10763,7 @@
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10795,7 +10797,7 @@
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M142" s="15" t="inlineStr">
@@ -10816,12 +10818,12 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
@@ -10831,7 +10833,7 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10861,22 +10863,22 @@
         <v>20</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M143" s="12" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N143" s="13" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O143" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P143" s="13" t="n">
@@ -10886,22 +10888,22 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -10914,7 +10916,7 @@
       </c>
       <c r="G144" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H144" s="15" t="inlineStr">
@@ -10924,21 +10926,29 @@
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L144" s="15" t="inlineStr"/>
-      <c r="M144" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L144" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M144" s="15" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N144" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O144" s="16" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O144" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P144" s="16" t="n">
@@ -10948,12 +10958,12 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-15041</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
@@ -10963,7 +10973,7 @@
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>CD38</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -10986,14 +10996,14 @@
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="L145" s="12" t="inlineStr"/>
       <c r="M145" s="12" t="inlineStr"/>
@@ -11010,22 +11020,22 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
@@ -11048,25 +11058,17 @@
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
         <v>28</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L146" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M146" s="15" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L146" s="15" t="inlineStr"/>
+      <c r="M146" s="15" t="inlineStr"/>
       <c r="N146" s="16" t="n">
         <v>0</v>
       </c>
@@ -11080,22 +11082,22 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
@@ -11118,17 +11120,25 @@
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L147" s="12" t="inlineStr"/>
-      <c r="M147" s="12" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L147" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M147" s="12" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N147" s="13" t="n">
         <v>0</v>
       </c>
@@ -11142,22 +11152,22 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E148" s="15" t="n">
@@ -11180,14 +11190,14 @@
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L148" s="15" t="inlineStr"/>
       <c r="M148" s="15" t="inlineStr"/>
@@ -11204,12 +11214,12 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
@@ -11219,7 +11229,7 @@
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
@@ -11237,19 +11247,19 @@
       </c>
       <c r="H149" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
         <v>33</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L149" s="12" t="inlineStr"/>
       <c r="M149" s="12" t="inlineStr"/>
@@ -11266,22 +11276,22 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E150" s="15" t="n">
@@ -11304,14 +11314,14 @@
       </c>
       <c r="I150" s="15" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J150" s="15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L150" s="15" t="inlineStr"/>
       <c r="M150" s="15" t="inlineStr"/>
@@ -11328,22 +11338,22 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E151" s="12" t="n">
@@ -11356,35 +11366,27 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H151" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I151" s="12" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J151" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L151" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M151" s="12" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L151" s="12" t="inlineStr"/>
+      <c r="M151" s="12" t="inlineStr"/>
       <c r="N151" s="13" t="n">
         <v>0</v>
       </c>
@@ -11398,22 +11400,22 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E152" s="15" t="n">
@@ -11426,23 +11428,35 @@
       </c>
       <c r="G152" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H152" s="15" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H152" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
         <v>35</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L152" s="15" t="inlineStr"/>
-      <c r="M152" s="15" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L152" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M152" s="15" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N152" s="16" t="n">
         <v>0</v>
       </c>
@@ -11456,12 +11470,12 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
@@ -11471,7 +11485,7 @@
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E153" s="12" t="n">
@@ -11487,14 +11501,10 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H153" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H153" s="12" t="inlineStr"/>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
@@ -11503,16 +11513,8 @@
       <c r="K153" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L153" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M153" s="12" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+      <c r="L153" s="12" t="inlineStr"/>
+      <c r="M153" s="12" t="inlineStr"/>
       <c r="N153" s="13" t="n">
         <v>0</v>
       </c>
@@ -11526,12 +11528,12 @@
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr">
@@ -11541,7 +11543,7 @@
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E154" s="15" t="n">
@@ -11564,17 +11566,25 @@
       </c>
       <c r="I154" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J154" s="15" t="n">
         <v>35</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L154" s="15" t="inlineStr"/>
-      <c r="M154" s="15" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L154" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M154" s="15" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N154" s="16" t="n">
         <v>0</v>
       </c>
@@ -11588,28 +11598,26 @@
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E155" s="12" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="n">
+        <v/>
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
@@ -11623,7 +11631,7 @@
       </c>
       <c r="H155" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I155" s="12" t="inlineStr">
@@ -11635,7 +11643,7 @@
         <v>35</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="L155" s="12" t="inlineStr"/>
       <c r="M155" s="12" t="inlineStr"/>
@@ -11652,23 +11660,27 @@
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C156" s="15" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C156" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E156" s="15" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F156" s="15" t="inlineStr">
@@ -11683,19 +11695,19 @@
       </c>
       <c r="H156" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J156" s="15" t="n">
         <v>35</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>11</v>
+        <v>1.25</v>
       </c>
       <c r="L156" s="15" t="inlineStr"/>
       <c r="M156" s="15" t="inlineStr"/>
@@ -11712,27 +11724,23 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
-        </is>
-      </c>
-      <c r="C157" s="12" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="inlineStr"/>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>MONTPELLIER MMM</t>
         </is>
       </c>
       <c r="E157" s="12" t="inlineStr">
         <is>
-          <t>Montée de version + Pastell</t>
+          <t>Déploiement Module AC</t>
         </is>
       </c>
       <c r="F157" s="12" t="inlineStr">
@@ -11747,19 +11755,19 @@
       </c>
       <c r="H157" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J157" s="12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>0.5</v>
+        <v>11</v>
       </c>
       <c r="L157" s="12" t="inlineStr"/>
       <c r="M157" s="12" t="inlineStr"/>
@@ -11776,21 +11784,29 @@
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="C158" s="15" t="inlineStr"/>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C158" s="15" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="E158" s="15" t="inlineStr"/>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E158" s="15" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
       <c r="F158" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11798,17 +11814,21 @@
       </c>
       <c r="G158" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H158" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H158" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J158" s="15" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K158" s="15" t="n">
         <v>0.5</v>
@@ -11828,18 +11848,18 @@
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr"/>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E159" s="12" t="inlineStr"/>
@@ -11856,14 +11876,14 @@
       <c r="H159" s="12" t="inlineStr"/>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J159" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L159" s="12" t="inlineStr"/>
       <c r="M159" s="12" t="inlineStr"/>
@@ -11880,18 +11900,18 @@
     <row r="160">
       <c r="A160" s="14" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C160" s="15" t="inlineStr"/>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E160" s="15" t="inlineStr"/>
@@ -11902,36 +11922,28 @@
       </c>
       <c r="G160" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H160" s="15" t="inlineStr"/>
       <c r="I160" s="15" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J160" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K160" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M160" s="15" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L160" s="15" t="inlineStr"/>
+      <c r="M160" s="15" t="inlineStr"/>
       <c r="N160" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O160" s="16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P160" s="16" t="n">
         <v>0</v>
@@ -11940,18 +11952,18 @@
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr"/>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E161" s="12" t="inlineStr"/>
@@ -11968,50 +11980,50 @@
       <c r="H161" s="12" t="inlineStr"/>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J161" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K161" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L161" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-34778</t>
         </is>
       </c>
       <c r="M161" s="12" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00172868</t>
         </is>
       </c>
       <c r="N161" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O161" s="13" t="n">
-        <v>595.7</v>
+        <v>100</v>
       </c>
       <c r="P161" s="13" t="n">
-        <v>595.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr"/>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E162" s="15" t="inlineStr"/>
@@ -12022,28 +12034,36 @@
       </c>
       <c r="G162" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H162" s="15" t="inlineStr"/>
       <c r="I162" s="15" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J162" s="15" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K162" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L162" s="15" t="inlineStr"/>
-      <c r="M162" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L162" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34335</t>
+        </is>
+      </c>
+      <c r="M162" s="15" t="inlineStr">
+        <is>
+          <t>00168072</t>
+        </is>
+      </c>
       <c r="N162" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O162" s="16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P162" s="16" t="n">
         <v>0</v>
@@ -12052,18 +12072,18 @@
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>PSC-583</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr"/>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E163" s="12" t="inlineStr"/>
@@ -12074,59 +12094,171 @@
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H163" s="12" t="inlineStr"/>
       <c r="I163" s="12" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J163" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K163" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L163" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M163" s="12" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N163" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" s="13" t="n">
+        <v>595.7</v>
+      </c>
+      <c r="P163" s="13" t="n">
+        <v>595.7</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="14" t="inlineStr">
+        <is>
+          <t>PSC-850</t>
+        </is>
+      </c>
+      <c r="B164" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="C164" s="15" t="inlineStr"/>
+      <c r="D164" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="E164" s="15" t="inlineStr"/>
+      <c r="F164" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G164" s="15" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H164" s="15" t="inlineStr"/>
+      <c r="I164" s="15" t="inlineStr">
+        <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="J164" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="K164" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L164" s="15" t="inlineStr"/>
+      <c r="M164" s="15" t="inlineStr"/>
+      <c r="N164" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="11" t="inlineStr">
+        <is>
+          <t>PSC-583</t>
+        </is>
+      </c>
+      <c r="B165" s="12" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="C165" s="12" t="inlineStr"/>
+      <c r="D165" s="12" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="E165" s="12" t="inlineStr"/>
+      <c r="F165" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G165" s="12" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H165" s="12" t="inlineStr"/>
+      <c r="I165" s="12" t="inlineStr">
+        <is>
           <t>20/03/2025</t>
         </is>
       </c>
-      <c r="J163" s="12" t="n">
+      <c r="J165" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K163" s="12" t="n">
+      <c r="K165" s="12" t="n">
         <v>0.25</v>
       </c>
-      <c r="L163" s="12" t="inlineStr"/>
-      <c r="M163" s="12" t="inlineStr"/>
-      <c r="N163" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O163" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P163" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="18" t="inlineStr">
+      <c r="L165" s="12" t="inlineStr"/>
+      <c r="M165" s="12" t="inlineStr"/>
+      <c r="N165" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B164" s="18" t="inlineStr"/>
-      <c r="C164" s="18" t="inlineStr"/>
-      <c r="D164" s="18" t="inlineStr"/>
-      <c r="E164" s="18" t="inlineStr"/>
-      <c r="F164" s="18" t="inlineStr"/>
-      <c r="G164" s="18" t="inlineStr"/>
-      <c r="H164" s="18" t="inlineStr"/>
-      <c r="I164" s="18" t="inlineStr"/>
-      <c r="J164" s="18" t="inlineStr"/>
-      <c r="K164" s="18" t="inlineStr"/>
-      <c r="L164" s="18" t="inlineStr"/>
-      <c r="M164" s="18" t="inlineStr"/>
-      <c r="N164" s="19" t="n">
+      <c r="B166" s="18" t="inlineStr"/>
+      <c r="C166" s="18" t="inlineStr"/>
+      <c r="D166" s="18" t="inlineStr"/>
+      <c r="E166" s="18" t="inlineStr"/>
+      <c r="F166" s="18" t="inlineStr"/>
+      <c r="G166" s="18" t="inlineStr"/>
+      <c r="H166" s="18" t="inlineStr"/>
+      <c r="I166" s="18" t="inlineStr"/>
+      <c r="J166" s="18" t="inlineStr"/>
+      <c r="K166" s="18" t="inlineStr"/>
+      <c r="L166" s="18" t="inlineStr"/>
+      <c r="M166" s="18" t="inlineStr"/>
+      <c r="N166" s="19" t="n">
         <v>46991.995</v>
       </c>
-      <c r="O164" s="19" t="n">
-        <v>40393.462</v>
-      </c>
-      <c r="P164" s="19" t="n">
-        <v>147.69</v>
+      <c r="O166" s="19" t="n">
+        <v>40643.462</v>
+      </c>
+      <c r="P166" s="19" t="n">
+        <v>148.6</v>
       </c>
     </row>
   </sheetData>
@@ -12291,6 +12423,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId161"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13140,13 +13274,13 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>362786</v>
+        <v>366386</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>134530</v>
+        <v>138205</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>228256</v>
+        <v>228181</v>
       </c>
       <c r="E5" s="25" t="n">
         <v>144874</v>
@@ -13165,13 +13299,13 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>164533</v>
+        <v>164283</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>60810</v>
+        <v>60635</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>103722</v>
+        <v>103647</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>86630</v>
@@ -13190,10 +13324,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>198253</v>
+        <v>202103</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>73719</v>
+        <v>77569</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>124534</v>
@@ -13337,7 +13471,7 @@
         </is>
       </c>
       <c r="I5" s="26" t="n">
-        <v>0</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="6">
@@ -13787,7 +13921,7 @@
         </is>
       </c>
       <c r="I15" s="26" t="n">
-        <v>0</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="16">
@@ -14078,7 +14212,7 @@
         </is>
       </c>
       <c r="I22" s="25" t="n">
-        <v>25202</v>
+        <v>29052</v>
       </c>
     </row>
     <row r="23">
@@ -14120,7 +14254,7 @@
         </is>
       </c>
       <c r="I24" s="25" t="n">
-        <v>15166</v>
+        <v>19016</v>
       </c>
     </row>
   </sheetData>
